--- a/docs/alliance-templates/alliance-brands.xlsx
+++ b/docs/alliance-templates/alliance-brands.xlsx
@@ -7,39 +7,77 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌内容" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'品牌内容'!$A$2:$C$2</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'Sheet1'!$A$1:$C$6</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>填写说明：
-* 必填列。
-品牌类型：talent（人才品牌） / employer（雇主品牌） / job（岗位品牌） / major（专业品牌） / teacher（教师品牌） / culture（文化品牌）
-名称：品牌名称
-描述：文本，选填</t>
-  </si>
-  <si>
-    <t>品牌类型 *</t>
-  </si>
-  <si>
-    <t>名称 *</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>品牌类型</t>
+  </si>
+  <si>
+    <t>名称</t>
   </si>
   <si>
     <t>描述</t>
+  </si>
+  <si>
+    <t>talent</t>
+  </si>
+  <si>
+    <t>优秀毕业生-张三</t>
+  </si>
+  <si>
+    <t>2025届软件工程专业，就职于华为，岗位AI算法工程师</t>
+  </si>
+  <si>
+    <t>employer</t>
+  </si>
+  <si>
+    <t>华为雇主品牌</t>
+  </si>
+  <si>
+    <t>全球领先ICT基础设施提供商，与我校共建AI实验室</t>
+  </si>
+  <si>
+    <t>job</t>
+  </si>
+  <si>
+    <t>AI算法工程师</t>
+  </si>
+  <si>
+    <t>人工智能方向核心岗位，平均薪资15-25K，需求旺盛</t>
+  </si>
+  <si>
+    <t>major</t>
+  </si>
+  <si>
+    <t>软件工程专业品牌</t>
+  </si>
+  <si>
+    <t>国家级一流本科专业，就业率98.5%，与华为等企业深度合作</t>
+  </si>
+  <si>
+    <t>teacher</t>
+  </si>
+  <si>
+    <t>刘建国教授</t>
+  </si>
+  <si>
+    <t>双师型教师，人工智能方向博士生导师，主持国家级项目</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,14 +87,8 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
       <sz val="11"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF808080"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,7 +100,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="FFCCE5FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,34 +112,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
-      <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -374,37 +390,84 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="true"/>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="2" min="1" width="28"/>
-    <col customWidth="true" max="3" min="3" width="48"/>
+    <col customWidth="true" max="1" min="1" width="14"/>
+    <col customWidth="true" max="2" min="2" width="28"/>
+    <col customWidth="true" max="3" min="3" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" ht="96" customHeight="true">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="24" customHeight="true">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-    </row>
-    <row r="2" ht="28" customHeight="true">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="2" ht="20" customHeight="true">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="true">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$2:$C$2"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
+  <autoFilter ref="$A$1:$C$6"/>
 </worksheet>
 </file>
--- a/docs/alliance-templates/alliance-brands.xlsx
+++ b/docs/alliance-templates/alliance-brands.xlsx
@@ -1,83 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌内容" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'Sheet1'!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'品牌内容'!$A$2:$C$2</definedName>
   </definedNames>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="122211" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
-  <si>
-    <t>品牌类型</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>talent</t>
-  </si>
-  <si>
-    <t>优秀毕业生-张三</t>
-  </si>
-  <si>
-    <t>2025届软件工程专业，就职于华为，岗位AI算法工程师</t>
-  </si>
-  <si>
-    <t>employer</t>
-  </si>
-  <si>
-    <t>华为雇主品牌</t>
-  </si>
-  <si>
-    <t>全球领先ICT基础设施提供商，与我校共建AI实验室</t>
-  </si>
-  <si>
-    <t>job</t>
-  </si>
-  <si>
-    <t>AI算法工程师</t>
-  </si>
-  <si>
-    <t>人工智能方向核心岗位，平均薪资15-25K，需求旺盛</t>
-  </si>
-  <si>
-    <t>major</t>
-  </si>
-  <si>
-    <t>软件工程专业品牌</t>
-  </si>
-  <si>
-    <t>国家级一流本科专业，就业率98.5%，与华为等企业深度合作</t>
-  </si>
-  <si>
-    <t>teacher</t>
-  </si>
-  <si>
-    <t>刘建国教授</t>
-  </si>
-  <si>
-    <t>双师型教师，人工智能方向博士生导师，主持国家级项目</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,13 +28,23 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -103,8 +54,20 @@
         <fgColor rgb="FFCCE5FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -113,24 +76,113 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -391,83 +443,139 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="true"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="14"/>
-    <col customWidth="true" max="2" min="2" width="28"/>
-    <col customWidth="true" max="3" min="3" width="50"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="true">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="true">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="true">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="true">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="true">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="true">
-      <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
+    <row r="1" ht="112" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>填写说明：
+* 必填列。
+品牌类型：talent（人才品牌） / employer（雇主品牌） / job（岗位品牌） / major（专业品牌） / teacher（教师品牌） / culture（文化品牌）
+名称：品牌名称
+描述：文本，选填</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>品牌类型 *</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>名称 *</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>talent</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>优秀毕业生-张三</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>2025届软件工程专业，就职于华为，岗位AI算法工程师</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>employer</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>华为雇主品牌</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>全球领先ICT基础设施提供商，与我校共建AI实验室</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>AI算法工程师</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>人工智能方向核心岗位，平均薪资15-25K，需求旺盛</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>软件工程专业品牌</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>国家级一流本科专业，就业率98.5%，与华为等企业深度合作</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>刘建国教授</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>双师型教师，人工智能方向博士生导师，主持国家级项目</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$C$6"/>
+  <autoFilter ref="A2:C2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/alliance-templates/alliance-brands.xlsx
+++ b/docs/alliance-templates/alliance-brands.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌内容" sheetId="1" state="visible" r:id="rId1"/>
@@ -67,7 +67,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -90,11 +90,55 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,6 +154,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -466,8 +512,8 @@
 描述：文本，选填</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="4" t="n"/>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="8" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -489,7 +535,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>talent</t>
+          <t>人才品牌</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -506,7 +552,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>employer</t>
+          <t>雇主品牌</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -523,7 +569,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>岗位品牌</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -540,7 +586,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>major</t>
+          <t>专业品牌</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -557,7 +603,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>teacher</t>
+          <t>师资品牌</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
